--- a/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0002T0006Z000C1N25_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0002T0006Z000C1N25_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>19.67289297841026</v>
+        <v>3.196845108991668</v>
       </c>
       <c r="D2" t="n">
-        <v>19.80684340061015</v>
+        <v>3.218612052599149</v>
       </c>
       <c r="E2" t="n">
-        <v>6.521038749771202</v>
+        <v>1.05966879683782</v>
       </c>
       <c r="F2" t="n">
-        <v>4.427001937808704</v>
+        <v>0.7193878148939145</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>18.48238442798435</v>
+        <v>3.003387469547457</v>
       </c>
       <c r="D3" t="n">
-        <v>14.47622457135083</v>
+        <v>2.35238649284451</v>
       </c>
       <c r="E3" t="n">
-        <v>6.521038749771202</v>
+        <v>1.05966879683782</v>
       </c>
       <c r="F3" t="n">
-        <v>4.427001937808704</v>
+        <v>0.7193878148939145</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.582806563792</v>
+        <v>3.6697060666162</v>
       </c>
       <c r="D4" t="n">
-        <v>14.92517025729579</v>
+        <v>2.425340166810566</v>
       </c>
       <c r="E4" t="n">
-        <v>6.521038749771202</v>
+        <v>1.05966879683782</v>
       </c>
       <c r="F4" t="n">
-        <v>4.427001937808704</v>
+        <v>0.7193878148939145</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.20764533271818</v>
+        <v>4.908742366566704</v>
       </c>
       <c r="D5" t="n">
-        <v>17.21581145341079</v>
+        <v>2.797569361179253</v>
       </c>
       <c r="E5" t="n">
-        <v>6.521038749771202</v>
+        <v>1.05966879683782</v>
       </c>
       <c r="F5" t="n">
-        <v>4.427001937808704</v>
+        <v>0.7193878148939145</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>20.66538288945307</v>
+        <v>3.358124719536124</v>
       </c>
       <c r="D6" t="n">
-        <v>20.85751272243588</v>
+        <v>3.38934581739583</v>
       </c>
       <c r="E6" t="n">
-        <v>6.521038749771202</v>
+        <v>1.05966879683782</v>
       </c>
       <c r="F6" t="n">
-        <v>4.427001937808704</v>
+        <v>0.7193878148939145</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>8.10726721000723</v>
+        <v>1.317430921626175</v>
       </c>
       <c r="D7" t="n">
-        <v>7.347812734312964</v>
+        <v>1.194019569325857</v>
       </c>
       <c r="E7" t="n">
-        <v>6.521038749771202</v>
+        <v>1.05966879683782</v>
       </c>
       <c r="F7" t="n">
-        <v>4.427001937808704</v>
+        <v>0.7193878148939145</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
